--- a/Result/checksun/油電燃氣業.xlsx
+++ b/Result/checksun/油電燃氣業.xlsx
@@ -723,7 +723,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -3895,7 +3895,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -4809,24 +4809,24 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>-6.0</t>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -5961,24 +5961,24 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>-5.0</t>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -7067,7 +7067,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7117,24 +7117,24 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>24.0</t>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -7693,24 +7693,24 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -7723,12 +7723,12 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -10239,7 +10239,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>多頭排列股</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -10607,12 +10607,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -10895,12 +10895,12 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -11471,12 +11471,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -11759,12 +11759,12 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -12335,12 +12335,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -13199,12 +13199,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -13411,7 +13411,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -13461,24 +13461,24 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -13491,12 +13491,12 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>72</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -13749,24 +13749,24 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>-2.0</t>
@@ -13779,12 +13779,12 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>72</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -14037,24 +14037,24 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>-1.0</t>
@@ -14067,12 +14067,12 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>72</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -14325,24 +14325,24 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O49" t="inlineStr">
         <is>
           <t>-4.0</t>
@@ -14355,94 +14355,94 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>-1.90</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>29.99</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>30.0425</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>30.623</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>15.78</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>33.33333333333333</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>33.33333333333333</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>-42.98</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>-1210116.6</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>-846347.1</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>-1.90</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>29.99</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>30.0425</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>30.623</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>15.78</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>33.33333333333333</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>33.33333333333333</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>-42.98</t>
-        </is>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>-1210116.6</t>
-        </is>
-      </c>
-      <c r="AG49" t="inlineStr">
-        <is>
-          <t>-846347.1</t>
-        </is>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="AI49" t="inlineStr">
         <is>
           <t>-10473.20058598843</t>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
@@ -14613,84 +14613,84 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>-1.97</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>30.643</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>14.58</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
           <t>-0.17</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>-1.97</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>30.04</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>30.643</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>14.58</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>-0.20</t>
@@ -14793,7 +14793,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -14931,12 +14931,12 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>72</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
@@ -15111,7 +15111,7 @@
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -15219,12 +15219,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>72</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -15477,94 +15477,94 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>30.0575</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>30.7</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>11.93</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>30.04</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>30.0575</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>11.93</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
           <t>16.66666666666667</t>
@@ -15657,7 +15657,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -15687,7 +15687,7 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -15795,12 +15795,12 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>72</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -15975,7 +15975,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -16053,94 +16053,94 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>-1.86</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>30.06</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>30.1775</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>30.749</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>9.55</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>-0.39</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>-1.86</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>30.06</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>30.1775</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>30.749</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>9.55</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AC55" t="inlineStr">
         <is>
           <t>33.33333333333334</t>
@@ -16233,7 +16233,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -16341,7 +16341,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>72</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -16521,7 +16521,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -16583,7 +16583,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -16633,27 +16633,27 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>-46.0</t>
+          <t>-27.0</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -16663,12 +16663,12 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>361</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -16838,12 +16838,12 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -16931,7 +16931,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -16941,7 +16941,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>-44.0</t>
+          <t>-25.0</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -16951,12 +16951,12 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>361</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -17101,7 +17101,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -17126,12 +17126,12 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -17189,7 +17189,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -17209,54 +17209,54 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
           <t>-0.19</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>-0.85</t>
@@ -17389,7 +17389,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
@@ -17414,12 +17414,12 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>60.77</t>
+          <t>35.18</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>88</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -17527,12 +17527,12 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>361</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -17687,7 +17687,7 @@
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -17702,12 +17702,12 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>49.28</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -17795,7 +17795,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>75</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -17815,12 +17815,12 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>361</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
@@ -17990,12 +17990,12 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -18053,7 +18053,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -18083,7 +18083,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>61</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -18093,7 +18093,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -18103,12 +18103,12 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>361</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -18253,7 +18253,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
@@ -18278,12 +18278,12 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>37.32</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -18371,7 +18371,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>49</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -18391,12 +18391,12 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>361</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
@@ -18566,12 +18566,12 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -18649,7 +18649,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -18659,7 +18659,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>38</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -18679,12 +18679,12 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>361</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -18839,7 +18839,7 @@
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
@@ -18854,12 +18854,12 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -18937,7 +18937,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -18967,12 +18967,12 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>361</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -19117,7 +19117,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
@@ -19142,12 +19142,12 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -19205,7 +19205,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -19225,29 +19225,29 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>價-量-</t>
@@ -19255,12 +19255,12 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>361</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -19415,7 +19415,7 @@
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
@@ -19430,12 +19430,12 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
@@ -19493,7 +19493,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>6.70</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -19543,12 +19543,12 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>361</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -19693,7 +19693,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
@@ -19718,12 +19718,12 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
@@ -19755,7 +19755,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -19805,99 +19805,99 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>-2.35</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>-9.54</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>38.70999999999999</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>39.64</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>43.82100000000001</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>-1.26</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>1572</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>-1.45</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>-2.35</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>-9.54</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>38.70999999999999</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>39.64</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>43.82100000000001</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>7.15</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>-1.26</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
+      <c r="AC68" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AD68" t="inlineStr">
         <is>
           <t>-58.96</t>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -19995,7 +19995,7 @@
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>190.75</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -20010,12 +20010,12 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
@@ -20093,7 +20093,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -20123,12 +20123,12 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>492</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>190.75</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
@@ -20298,12 +20298,12 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -20411,12 +20411,12 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>492</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -20571,7 +20571,7 @@
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>190.75</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -20586,12 +20586,12 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -20669,7 +20669,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -20699,12 +20699,12 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>492</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -20859,7 +20859,7 @@
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>190.75</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
@@ -20874,12 +20874,12 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -20987,12 +20987,12 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>492</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>190.75</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
@@ -21162,12 +21162,12 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
@@ -21245,7 +21245,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -21275,12 +21275,12 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>492</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -21425,7 +21425,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>190.75</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
@@ -21450,12 +21450,12 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -21563,12 +21563,12 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>492</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -21713,7 +21713,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -21723,7 +21723,7 @@
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>190.75</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
@@ -21738,12 +21738,12 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -21821,7 +21821,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>-12.98</t>
+          <t>-13.42</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -21851,12 +21851,12 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>492</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -22001,7 +22001,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>190.75</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
@@ -22026,12 +22026,12 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -22139,12 +22139,12 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>492</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -22289,7 +22289,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>190.75</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -22427,12 +22427,12 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>492</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -22577,7 +22577,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>190.75</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
@@ -22602,12 +22602,12 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -22715,12 +22715,12 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>492</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>190.75</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
@@ -22927,7 +22927,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -22977,24 +22977,24 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O79" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -23007,12 +23007,12 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>788</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -23157,7 +23157,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -23167,7 +23167,7 @@
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
@@ -23187,7 +23187,7 @@
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
@@ -23265,7 +23265,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -23295,12 +23295,12 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>788</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -23445,7 +23445,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -23455,7 +23455,7 @@
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
@@ -23475,7 +23475,7 @@
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -23553,7 +23553,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -23583,12 +23583,12 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>788</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -23733,7 +23733,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -23743,7 +23743,7 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
@@ -23841,7 +23841,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -23871,12 +23871,12 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>788</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -24021,7 +24021,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -24031,7 +24031,7 @@
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
@@ -24129,7 +24129,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -24159,12 +24159,12 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>788</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -24309,7 +24309,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -24319,7 +24319,7 @@
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -24447,12 +24447,12 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>788</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -24597,7 +24597,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -24607,7 +24607,7 @@
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -24735,12 +24735,12 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>788</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -24895,7 +24895,7 @@
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
@@ -24915,7 +24915,7 @@
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
@@ -24993,24 +24993,24 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O86" t="inlineStr">
         <is>
           <t>-1.0</t>
@@ -25023,12 +25023,12 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>788</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -25173,7 +25173,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -25183,7 +25183,7 @@
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -25203,7 +25203,7 @@
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
@@ -25281,7 +25281,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -25311,12 +25311,12 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>788</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -25461,7 +25461,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
@@ -25491,7 +25491,7 @@
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
@@ -25569,7 +25569,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -25599,12 +25599,12 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>788</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -25749,7 +25749,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
@@ -25779,7 +25779,7 @@
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
@@ -25857,7 +25857,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -25887,12 +25887,12 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>788</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -26037,7 +26037,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
@@ -26099,7 +26099,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -26184,7 +26184,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
@@ -26472,7 +26472,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -26642,7 +26642,7 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
@@ -26760,7 +26760,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -26930,7 +26930,7 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
@@ -27048,7 +27048,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -27218,7 +27218,7 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -27506,7 +27506,7 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
@@ -27624,7 +27624,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -27794,7 +27794,7 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
@@ -27912,7 +27912,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -28082,7 +28082,7 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
@@ -28200,7 +28200,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -28370,7 +28370,7 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
@@ -28488,7 +28488,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
@@ -28776,7 +28776,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -28946,7 +28946,7 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -29234,7 +29234,7 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
@@ -29271,7 +29271,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -29321,24 +29321,24 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O101" t="inlineStr">
         <is>
           <t>-5.0</t>
@@ -29351,12 +29351,12 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -29501,7 +29501,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -29511,7 +29511,7 @@
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
@@ -29526,12 +29526,12 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
@@ -29609,7 +29609,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -29639,12 +29639,12 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -29789,7 +29789,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -29799,7 +29799,7 @@
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
@@ -29814,12 +29814,12 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
@@ -29897,7 +29897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -29927,12 +29927,12 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -30077,7 +30077,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -30087,7 +30087,7 @@
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
@@ -30102,12 +30102,12 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
@@ -30185,7 +30185,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -30215,12 +30215,12 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -30365,7 +30365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -30375,7 +30375,7 @@
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
@@ -30390,12 +30390,12 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
@@ -30473,7 +30473,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -30503,12 +30503,12 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -30653,7 +30653,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -30663,7 +30663,7 @@
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
@@ -30678,12 +30678,12 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
@@ -30761,7 +30761,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -30791,12 +30791,12 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -30941,7 +30941,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -30951,7 +30951,7 @@
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
@@ -30966,12 +30966,12 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -31079,12 +31079,12 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -31229,7 +31229,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -31239,7 +31239,7 @@
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
@@ -31254,12 +31254,12 @@
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -31367,12 +31367,12 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -31517,7 +31517,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -31527,7 +31527,7 @@
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
@@ -31542,12 +31542,12 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
@@ -31625,7 +31625,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -31655,12 +31655,12 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -31805,7 +31805,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -31815,7 +31815,7 @@
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
@@ -31830,12 +31830,12 @@
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
@@ -31913,7 +31913,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -31943,12 +31943,12 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -32093,7 +32093,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -32103,7 +32103,7 @@
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
@@ -32118,12 +32118,12 @@
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
@@ -32201,7 +32201,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -32231,12 +32231,12 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -32381,7 +32381,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -32391,7 +32391,7 @@
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
@@ -32406,12 +32406,12 @@
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
@@ -32443,7 +32443,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>弱勢突破股</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -32493,7 +32493,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -32523,12 +32523,12 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -32673,7 +32673,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -32703,7 +32703,7 @@
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>377228</t>
+          <t>375799</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
@@ -32781,7 +32781,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -32811,12 +32811,12 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -32961,7 +32961,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -32991,7 +32991,7 @@
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>377228</t>
+          <t>375799</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
@@ -33069,7 +33069,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -33099,12 +33099,12 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -33249,7 +33249,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -33279,7 +33279,7 @@
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>377228</t>
+          <t>375799</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
@@ -33357,7 +33357,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -33387,12 +33387,12 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -33537,7 +33537,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -33567,7 +33567,7 @@
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>377228</t>
+          <t>375799</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
@@ -33645,7 +33645,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -33675,12 +33675,12 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -33825,7 +33825,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>377228</t>
+          <t>375799</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
@@ -33933,7 +33933,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -33963,12 +33963,12 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -34113,7 +34113,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -34143,7 +34143,7 @@
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>377228</t>
+          <t>375799</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
@@ -34221,7 +34221,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -34251,12 +34251,12 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -34401,7 +34401,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -34431,7 +34431,7 @@
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>377228</t>
+          <t>375799</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
@@ -34509,7 +34509,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>-7.45</t>
+          <t>-7.86</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -34539,12 +34539,12 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -34719,7 +34719,7 @@
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>377228</t>
+          <t>375799</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
@@ -34797,7 +34797,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>-8.96</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -34827,12 +34827,12 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -34977,7 +34977,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -35007,7 +35007,7 @@
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>377228</t>
+          <t>375799</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
@@ -35085,7 +35085,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>-9.72</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -35115,12 +35115,12 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -35265,7 +35265,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>377228</t>
+          <t>375799</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
@@ -35373,7 +35373,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>-8.33</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -35403,12 +35403,12 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -35553,7 +35553,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -35583,7 +35583,7 @@
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>377228</t>
+          <t>375799</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
@@ -35615,7 +35615,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>建議關注股</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -35695,12 +35695,12 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -35800,7 +35800,7 @@
       </c>
       <c r="AL123" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM123" t="inlineStr">
@@ -35845,7 +35845,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -35875,7 +35875,7 @@
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
@@ -35953,24 +35953,24 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="O124" t="inlineStr">
         <is>
           <t>5.0</t>
@@ -35983,12 +35983,12 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -36088,7 +36088,7 @@
       </c>
       <c r="AL124" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
@@ -36133,7 +36133,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -36163,7 +36163,7 @@
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
@@ -36241,7 +36241,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -36271,12 +36271,12 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -36421,7 +36421,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -36451,7 +36451,7 @@
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
@@ -36529,7 +36529,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -36559,12 +36559,12 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -36709,7 +36709,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -36739,7 +36739,7 @@
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
@@ -36817,7 +36817,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -36847,12 +36847,12 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -36997,7 +36997,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -37027,7 +37027,7 @@
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
@@ -37105,7 +37105,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -37135,12 +37135,12 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -37285,7 +37285,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -37315,7 +37315,7 @@
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
@@ -37393,7 +37393,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -37423,12 +37423,12 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -37573,7 +37573,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -37603,7 +37603,7 @@
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
@@ -37681,7 +37681,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -37711,12 +37711,12 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -37861,7 +37861,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -37891,7 +37891,7 @@
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
@@ -37969,7 +37969,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -37999,12 +37999,12 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -38149,7 +38149,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -38179,7 +38179,7 @@
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
@@ -38257,7 +38257,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -38287,12 +38287,12 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -38437,7 +38437,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -38467,7 +38467,7 @@
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
@@ -38545,7 +38545,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -38575,12 +38575,12 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -38725,7 +38725,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -38755,7 +38755,7 @@
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">

--- a/Result/checksun/油電燃氣業.xlsx
+++ b/Result/checksun/油電燃氣業.xlsx
@@ -1013,7 +1013,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -1301,7 +1305,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -1589,7 +1597,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -1877,7 +1889,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -2165,7 +2181,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -2453,7 +2473,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -2741,7 +2765,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -3029,7 +3057,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -3317,7 +3349,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -3605,7 +3641,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -4185,7 +4225,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -4473,7 +4517,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -4761,7 +4809,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -5049,7 +5101,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -5337,7 +5393,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -5625,7 +5685,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -5913,7 +5977,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -6201,7 +6269,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -6489,7 +6561,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -6777,7 +6853,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -7357,7 +7437,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -7645,7 +7729,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -7933,7 +8021,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -8221,7 +8313,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -8509,7 +8605,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -8797,7 +8897,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -9085,7 +9189,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -9373,7 +9481,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -9661,7 +9773,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -9949,7 +10065,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -10529,7 +10649,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -10817,7 +10941,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -11105,7 +11233,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -11393,7 +11525,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -11681,7 +11817,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -11969,7 +12109,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -12257,7 +12401,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -12545,7 +12693,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -12833,7 +12985,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -13121,7 +13277,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -13701,7 +13861,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -13989,7 +14153,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -14277,7 +14445,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -14565,7 +14737,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -14853,7 +15029,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -15141,7 +15321,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -15429,7 +15613,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -15717,7 +15905,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -16005,7 +16197,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -16293,7 +16489,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -16873,7 +17073,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -17161,7 +17365,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -17449,7 +17657,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -17737,7 +17949,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -18025,7 +18241,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -18313,7 +18533,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -18601,7 +18825,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -18889,7 +19117,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -19177,7 +19409,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -19465,7 +19701,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -20045,7 +20285,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -20333,7 +20577,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -20621,7 +20869,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -20909,7 +21161,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -21197,7 +21453,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -21485,7 +21745,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -21773,7 +22037,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -22061,7 +22329,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -22349,7 +22621,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -22637,7 +22913,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -23217,7 +23497,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -23505,7 +23789,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -23793,7 +24081,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -24081,7 +24373,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -24369,7 +24665,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -24657,7 +24957,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -24945,7 +25249,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -25233,7 +25541,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -25521,7 +25833,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -25809,7 +26125,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -26389,7 +26709,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -26677,7 +27001,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -26965,7 +27293,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -27253,7 +27585,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -27541,7 +27877,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -27829,7 +28169,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -28117,7 +28461,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -28405,7 +28753,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -28693,7 +29045,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -28981,7 +29337,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -29561,7 +29921,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -29849,7 +30213,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -30137,7 +30505,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -30425,7 +30797,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -30713,7 +31089,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -31001,7 +31381,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -31289,7 +31673,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -31577,7 +31965,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -31865,7 +32257,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -32153,7 +32549,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -32733,7 +33133,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -33021,7 +33425,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -33309,7 +33717,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -33597,7 +34009,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -33885,7 +34301,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -34173,7 +34593,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -34461,7 +34885,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -34749,7 +35177,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -35037,7 +35469,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -35325,7 +35761,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -35905,7 +36345,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -36193,7 +36637,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -36481,7 +36929,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -36769,7 +37221,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -37057,7 +37513,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -37345,7 +37805,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -37633,7 +38097,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -37921,7 +38389,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -38209,7 +38681,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -38497,7 +38973,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>2025-08-25</t>

--- a/Result/checksun/油電燃氣業.xlsx
+++ b/Result/checksun/油電燃氣業.xlsx
@@ -1011,15 +1011,11 @@
           <t>59.36999999999999</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>60.768</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>62.19125</t>
-        </is>
+      <c r="AN2" t="n">
+        <v>60.768</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>62.19125</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -1398,15 +1394,11 @@
           <t>59.59500000000001</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>60.856</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>62.29875</t>
-        </is>
+      <c r="AN3" t="n">
+        <v>60.856</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>62.29875</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1785,15 +1777,11 @@
           <t>59.795</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>60.93599999999999</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>62.3975</t>
-        </is>
+      <c r="AN4" t="n">
+        <v>60.93599999999999</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>62.3975</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -2172,15 +2160,11 @@
           <t>59.995</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>61.03</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>62.4975</t>
-        </is>
+      <c r="AN5" t="n">
+        <v>61.03</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>62.4975</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -2559,15 +2543,11 @@
           <t>60.165</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>61.12200000000001</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>62.60374999999999</t>
-        </is>
+      <c r="AN6" t="n">
+        <v>61.12200000000001</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>62.60374999999999</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -2946,15 +2926,11 @@
           <t>60.4</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>61.23200000000001</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>62.72874999999999</t>
-        </is>
+      <c r="AN7" t="n">
+        <v>61.23200000000001</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>62.72874999999999</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -3333,15 +3309,11 @@
           <t>60.64</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>61.34200000000001</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>62.84625</t>
-        </is>
+      <c r="AN8" t="n">
+        <v>61.34200000000001</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>62.84625</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -3720,15 +3692,11 @@
           <t>60.92999999999999</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>61.472</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>62.96124999999999</t>
-        </is>
+      <c r="AN9" t="n">
+        <v>61.472</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>62.96124999999999</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -4107,15 +4075,11 @@
           <t>61.125</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>61.578</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>63.04</t>
-        </is>
+      <c r="AN10" t="n">
+        <v>61.578</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>63.04</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -4494,15 +4458,11 @@
           <t>61.29</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>61.68599999999999</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>63.11125000000001</t>
-        </is>
+      <c r="AN11" t="n">
+        <v>61.68599999999999</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>63.11125000000001</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -4881,15 +4841,11 @@
           <t>33.785</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>33.913</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>34.085625</t>
-        </is>
+      <c r="AN12" t="n">
+        <v>33.913</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>34.085625</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -5268,15 +5224,11 @@
           <t>33.7925</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>33.915</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>34.096875</t>
-        </is>
+      <c r="AN13" t="n">
+        <v>33.915</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>34.096875</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -5655,15 +5607,11 @@
           <t>33.8225</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>33.928</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>34.121875</t>
-        </is>
+      <c r="AN14" t="n">
+        <v>33.928</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>34.121875</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -6042,15 +5990,11 @@
           <t>33.86</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>33.945</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>34.14</t>
-        </is>
+      <c r="AN15" t="n">
+        <v>33.945</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>34.14</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -6429,15 +6373,11 @@
           <t>33.895</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>33.96</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>34.1625</t>
-        </is>
+      <c r="AN16" t="n">
+        <v>33.96</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>34.1625</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -6816,15 +6756,11 @@
           <t>33.9125</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>33.96899999999999</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>34.18125</t>
-        </is>
+      <c r="AN17" t="n">
+        <v>33.96899999999999</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>34.18125</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -7203,15 +7139,11 @@
           <t>33.9225</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>33.982</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>34.1875</t>
-        </is>
+      <c r="AN18" t="n">
+        <v>33.982</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>34.1875</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -7590,15 +7522,11 @@
           <t>33.9225</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>33.984</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>34.1875</t>
-        </is>
+      <c r="AN19" t="n">
+        <v>33.984</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>34.1875</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -7977,15 +7905,11 @@
           <t>33.935</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>33.99299999999999</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>34.1925</t>
-        </is>
+      <c r="AN20" t="n">
+        <v>33.99299999999999</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>34.1925</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -8364,15 +8288,11 @@
           <t>33.9475</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>34.19750000000001</t>
-        </is>
+      <c r="AN21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>34.19750000000001</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -8751,15 +8671,11 @@
           <t>49.8875</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>50.025</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>50.344375</t>
-        </is>
+      <c r="AN22" t="n">
+        <v>50.025</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>50.344375</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -9138,15 +9054,11 @@
           <t>49.9275</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>50.03099999999999</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>50.375625</t>
-        </is>
+      <c r="AN23" t="n">
+        <v>50.03099999999999</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>50.375625</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -9525,15 +9437,11 @@
           <t>49.9425</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>50.04600000000001</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>50.41125</t>
-        </is>
+      <c r="AN24" t="n">
+        <v>50.04600000000001</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>50.41125</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -9912,15 +9820,11 @@
           <t>49.95</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>50.056</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>50.44</t>
-        </is>
+      <c r="AN25" t="n">
+        <v>50.056</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>50.44</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -10299,15 +10203,11 @@
           <t>49.955</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>50.066</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>50.4725</t>
-        </is>
+      <c r="AN26" t="n">
+        <v>50.066</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>50.4725</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -10686,15 +10586,11 @@
           <t>49.9675</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>50.07900000000001</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>50.510625</t>
-        </is>
+      <c r="AN27" t="n">
+        <v>50.07900000000001</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>50.510625</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -11073,15 +10969,11 @@
           <t>50.0025</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>50.091</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>50.539375</t>
-        </is>
+      <c r="AN28" t="n">
+        <v>50.091</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>50.539375</v>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
@@ -11460,15 +11352,11 @@
           <t>50.0125</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>50.098</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>50.57125000000001</t>
-        </is>
+      <c r="AN29" t="n">
+        <v>50.098</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>50.57125000000001</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -11847,15 +11735,11 @@
           <t>50.0225</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>50.111</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>50.595625</t>
-        </is>
+      <c r="AN30" t="n">
+        <v>50.111</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>50.595625</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -12234,15 +12118,11 @@
           <t>50.0375</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>50.123</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>50.625625</t>
-        </is>
+      <c r="AN31" t="n">
+        <v>50.123</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>50.625625</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -12621,15 +12501,11 @@
           <t>39.505</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>39.64</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>39.92375</t>
-        </is>
+      <c r="AN32" t="n">
+        <v>39.64</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>39.92375</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -13008,15 +12884,11 @@
           <t>39.535</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>39.654</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>39.9375</t>
-        </is>
+      <c r="AN33" t="n">
+        <v>39.654</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>39.9375</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -13395,15 +13267,11 @@
           <t>39.53</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>39.672</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>39.955</t>
-        </is>
+      <c r="AN34" t="n">
+        <v>39.672</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>39.955</v>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
@@ -13782,15 +13650,11 @@
           <t>39.5225</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>39.691</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>39.965625</t>
-        </is>
+      <c r="AN35" t="n">
+        <v>39.691</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>39.965625</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
@@ -14169,15 +14033,11 @@
           <t>39.52</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>39.715</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>39.979375</t>
-        </is>
+      <c r="AN36" t="n">
+        <v>39.715</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>39.979375</v>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -14556,15 +14416,11 @@
           <t>39.535</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>39.735</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>39.996875</t>
-        </is>
+      <c r="AN37" t="n">
+        <v>39.735</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>39.996875</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -14943,15 +14799,11 @@
           <t>39.5325</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>39.748</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>40.000625</t>
-        </is>
+      <c r="AN38" t="n">
+        <v>39.748</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>40.000625</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -15330,15 +15182,11 @@
           <t>39.53</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>39.761</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>40.009375</t>
-        </is>
+      <c r="AN39" t="n">
+        <v>39.761</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>40.009375</v>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -15717,15 +15565,11 @@
           <t>39.5375</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>39.785</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>40.019375</t>
-        </is>
+      <c r="AN40" t="n">
+        <v>39.785</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>40.019375</v>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
@@ -16104,15 +15948,11 @@
           <t>39.5525</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>39.811</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>40.0275</t>
-        </is>
+      <c r="AN41" t="n">
+        <v>39.811</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>40.0275</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
@@ -16491,15 +16331,11 @@
           <t>29.975</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>30.01</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>30.234375</t>
-        </is>
+      <c r="AN42" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>30.234375</v>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
@@ -16878,15 +16714,11 @@
           <t>29.98</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>30.012</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>30.25</t>
-        </is>
+      <c r="AN43" t="n">
+        <v>30.012</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>30.25</v>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
@@ -17265,15 +17097,11 @@
           <t>29.985</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>30.015</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>30.2675</t>
-        </is>
+      <c r="AN44" t="n">
+        <v>30.015</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>30.2675</v>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
@@ -17652,15 +17480,11 @@
           <t>29.99</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>30.018</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>30.284375</t>
-        </is>
+      <c r="AN45" t="n">
+        <v>30.018</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>30.284375</v>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
@@ -18039,15 +17863,11 @@
           <t>29.9925</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>30.021</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>30.29875</t>
-        </is>
+      <c r="AN46" t="n">
+        <v>30.021</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>30.29875</v>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
@@ -18426,15 +18246,11 @@
           <t>29.9925</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>30.023</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>30.316875</t>
-        </is>
+      <c r="AN47" t="n">
+        <v>30.023</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>30.316875</v>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
@@ -18813,15 +18629,11 @@
           <t>29.9975</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>30.025</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>30.334375</t>
-        </is>
+      <c r="AN48" t="n">
+        <v>30.025</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>30.334375</v>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
@@ -19200,15 +19012,11 @@
           <t>30.0</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>30.026</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
+      <c r="AN49" t="n">
+        <v>30.026</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>30.35</v>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
@@ -19587,15 +19395,11 @@
           <t>30.005</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>30.03</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>30.3675</t>
-        </is>
+      <c r="AN50" t="n">
+        <v>30.03</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>30.3675</v>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
@@ -19974,15 +19778,11 @@
           <t>30.005</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>30.031</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>30.383125</t>
-        </is>
+      <c r="AN51" t="n">
+        <v>30.031</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>30.383125</v>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
@@ -20361,15 +20161,11 @@
           <t>51.795</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>52.404</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>52.37375000000001</t>
-        </is>
+      <c r="AN52" t="n">
+        <v>52.404</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>52.37375000000001</v>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
@@ -20748,15 +20544,11 @@
           <t>51.88</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>52.428</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>52.39625000000001</t>
-        </is>
+      <c r="AN53" t="n">
+        <v>52.428</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>52.39625000000001</v>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
@@ -21135,15 +20927,11 @@
           <t>51.94</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>52.44</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>52.4125</t>
-        </is>
+      <c r="AN54" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>52.4125</v>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
@@ -21522,15 +21310,11 @@
           <t>51.985</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>52.444</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>52.42749999999999</t>
-        </is>
+      <c r="AN55" t="n">
+        <v>52.444</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>52.42749999999999</v>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
@@ -21909,15 +21693,11 @@
           <t>52.04499999999999</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>52.456</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>52.45124999999999</t>
-        </is>
+      <c r="AN56" t="n">
+        <v>52.456</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>52.45124999999999</v>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
@@ -22296,15 +22076,11 @@
           <t>52.11499999999999</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>52.46200000000001</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>52.47125</t>
-        </is>
+      <c r="AN57" t="n">
+        <v>52.46200000000001</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>52.47125</v>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
@@ -22683,15 +22459,11 @@
           <t>52.2</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>52.46400000000001</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>52.48999999999999</t>
-        </is>
+      <c r="AN58" t="n">
+        <v>52.46400000000001</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>52.48999999999999</v>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
@@ -23070,15 +22842,11 @@
           <t>52.315</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>52.474</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>52.51375</t>
-        </is>
+      <c r="AN59" t="n">
+        <v>52.474</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>52.51375</v>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
@@ -23457,15 +23225,11 @@
           <t>52.44</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>52.48</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>52.54</t>
-        </is>
+      <c r="AN60" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>52.54</v>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
@@ -23844,15 +23608,11 @@
           <t>52.565</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>52.48</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>52.565</t>
-        </is>
+      <c r="AN61" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>52.565</v>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
@@ -24231,15 +23991,11 @@
           <t>28.6175</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>34.252</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>38.049375</t>
-        </is>
+      <c r="AN62" t="n">
+        <v>34.252</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>38.049375</v>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
@@ -24618,15 +24374,11 @@
           <t>29.23250000000001</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>34.515</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>38.318125</t>
-        </is>
+      <c r="AN63" t="n">
+        <v>34.515</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>38.318125</v>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
@@ -25005,15 +24757,11 @@
           <t>29.8075</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>34.776</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>38.60062499999999</t>
-        </is>
+      <c r="AN64" t="n">
+        <v>34.776</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>38.60062499999999</v>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
@@ -25392,15 +25140,11 @@
           <t>30.4125</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>35.045</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>38.894375</t>
-        </is>
+      <c r="AN65" t="n">
+        <v>35.045</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>38.894375</v>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
@@ -25779,15 +25523,11 @@
           <t>30.9325</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>35.304</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>39.1875</t>
-        </is>
+      <c r="AN66" t="n">
+        <v>35.304</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>39.1875</v>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
@@ -26166,15 +25906,11 @@
           <t>31.4375</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>35.558</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>39.473125</t>
-        </is>
+      <c r="AN67" t="n">
+        <v>35.558</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>39.473125</v>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
@@ -26553,15 +26289,11 @@
           <t>31.915</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>35.804</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>39.755625</t>
-        </is>
+      <c r="AN68" t="n">
+        <v>35.804</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>39.755625</v>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
@@ -26940,15 +26672,11 @@
           <t>32.3125</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>36.04600000000001</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>40.00687499999999</t>
-        </is>
+      <c r="AN69" t="n">
+        <v>36.04600000000001</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>40.00687499999999</v>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
@@ -27327,15 +27055,11 @@
           <t>32.6675</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>36.304</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>40.260625</t>
-        </is>
+      <c r="AN70" t="n">
+        <v>36.304</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>40.260625</v>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
@@ -27714,15 +27438,11 @@
           <t>33.06</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>36.575</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>40.521875</t>
-        </is>
+      <c r="AN71" t="n">
+        <v>36.575</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>40.521875</v>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
@@ -28101,15 +27821,11 @@
           <t>48.7425</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>47.703</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>46.499375</t>
-        </is>
+      <c r="AN72" t="n">
+        <v>47.703</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>46.499375</v>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
@@ -28488,15 +28204,11 @@
           <t>48.7125</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>47.673</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
+      <c r="AN73" t="n">
+        <v>47.673</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>46.43</v>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
@@ -28875,15 +28587,11 @@
           <t>48.6625</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>47.655</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>46.360625</t>
-        </is>
+      <c r="AN74" t="n">
+        <v>47.655</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>46.360625</v>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
@@ -29262,15 +28970,11 @@
           <t>48.605</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>47.615</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>46.29125</t>
-        </is>
+      <c r="AN75" t="n">
+        <v>47.615</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>46.29125</v>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
@@ -29649,15 +29353,11 @@
           <t>48.53</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>47.575</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>46.218125</t>
-        </is>
+      <c r="AN76" t="n">
+        <v>47.575</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>46.218125</v>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
@@ -30036,15 +29736,11 @@
           <t>48.4225</t>
         </is>
       </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>47.527</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>46.13875</t>
-        </is>
+      <c r="AN77" t="n">
+        <v>47.527</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>46.13875</v>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
@@ -30423,15 +30119,11 @@
           <t>48.215</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>47.451</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>46.069375</t>
-        </is>
+      <c r="AN78" t="n">
+        <v>47.451</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>46.069375</v>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
@@ -30810,15 +30502,11 @@
           <t>48.0</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>47.353</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>46.008125</t>
-        </is>
+      <c r="AN79" t="n">
+        <v>47.353</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>46.008125</v>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
@@ -31197,15 +30885,11 @@
           <t>47.8075</t>
         </is>
       </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>47.248</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>45.948125</t>
-        </is>
+      <c r="AN80" t="n">
+        <v>47.248</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>45.948125</v>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
@@ -31584,15 +31268,11 @@
           <t>47.58499999999999</t>
         </is>
       </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>47.15600000000001</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>45.891875</t>
-        </is>
+      <c r="AN81" t="n">
+        <v>47.15600000000001</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>45.891875</v>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
@@ -31971,15 +31651,11 @@
           <t>59.38500000000001</t>
         </is>
       </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>60.386</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>60.36875</t>
-        </is>
+      <c r="AN82" t="n">
+        <v>60.386</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>60.36875</v>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
@@ -32358,15 +32034,11 @@
           <t>59.46</t>
         </is>
       </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>60.35625</t>
-        </is>
+      <c r="AN83" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>60.35625</v>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
@@ -32745,15 +32417,11 @@
           <t>59.575</t>
         </is>
       </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>60.452</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>60.375</t>
-        </is>
+      <c r="AN84" t="n">
+        <v>60.452</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>60.375</v>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
@@ -33132,15 +32800,11 @@
           <t>59.67999999999999</t>
         </is>
       </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>60.506</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>60.39624999999999</t>
-        </is>
+      <c r="AN85" t="n">
+        <v>60.506</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>60.39624999999999</v>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
@@ -33519,15 +33183,11 @@
           <t>59.79</t>
         </is>
       </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>60.578</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>60.42625</t>
-        </is>
+      <c r="AN86" t="n">
+        <v>60.578</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>60.42625</v>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
@@ -33906,15 +33566,11 @@
           <t>59.92</t>
         </is>
       </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>60.642</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>60.4625</t>
-        </is>
+      <c r="AN87" t="n">
+        <v>60.642</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>60.4625</v>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
@@ -34293,15 +33949,11 @@
           <t>60.015</t>
         </is>
       </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>60.70399999999999</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>60.4875</t>
-        </is>
+      <c r="AN88" t="n">
+        <v>60.70399999999999</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>60.4875</v>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
@@ -34680,15 +34332,11 @@
           <t>60.06</t>
         </is>
       </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>60.728</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
+      <c r="AN89" t="n">
+        <v>60.728</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>60.5</v>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
@@ -35067,15 +34715,11 @@
           <t>60.11499999999999</t>
         </is>
       </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>60.752</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>60.5125</t>
-        </is>
+      <c r="AN90" t="n">
+        <v>60.752</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>60.5125</v>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
@@ -35454,15 +35098,11 @@
           <t>60.185</t>
         </is>
       </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>60.768</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>60.525</t>
-        </is>
+      <c r="AN91" t="n">
+        <v>60.768</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>60.525</v>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
@@ -35841,15 +35481,11 @@
           <t>40.6675</t>
         </is>
       </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>41.242</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>41.714375</t>
-        </is>
+      <c r="AN92" t="n">
+        <v>41.242</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>41.714375</v>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
@@ -36228,15 +35864,11 @@
           <t>40.6825</t>
         </is>
       </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>41.27400000000001</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>41.729375</t>
-        </is>
+      <c r="AN93" t="n">
+        <v>41.27400000000001</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>41.729375</v>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
@@ -36615,15 +36247,11 @@
           <t>40.7</t>
         </is>
       </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>41.305</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>41.75</t>
-        </is>
+      <c r="AN94" t="n">
+        <v>41.305</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>41.75</v>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
@@ -37002,15 +36630,11 @@
           <t>40.7175</t>
         </is>
       </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>41.33600000000001</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>41.769375</t>
-        </is>
+      <c r="AN95" t="n">
+        <v>41.33600000000001</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>41.769375</v>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
@@ -37389,15 +37013,11 @@
           <t>40.7325</t>
         </is>
       </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>41.363</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>41.791875</t>
-        </is>
+      <c r="AN96" t="n">
+        <v>41.363</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>41.791875</v>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
@@ -37776,15 +37396,11 @@
           <t>40.76000000000001</t>
         </is>
       </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>41.397</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>41.80687500000001</t>
-        </is>
+      <c r="AN97" t="n">
+        <v>41.397</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>41.80687500000001</v>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
@@ -38163,15 +37779,11 @@
           <t>40.79</t>
         </is>
       </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>41.432</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>41.82375</t>
-        </is>
+      <c r="AN98" t="n">
+        <v>41.432</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>41.82375</v>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
@@ -38550,15 +38162,11 @@
           <t>40.83499999999999</t>
         </is>
       </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>41.47600000000001</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>41.844375</t>
-        </is>
+      <c r="AN99" t="n">
+        <v>41.47600000000001</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>41.844375</v>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
@@ -38937,15 +38545,11 @@
           <t>40.86499999999999</t>
         </is>
       </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>41.528</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>41.864375</t>
-        </is>
+      <c r="AN100" t="n">
+        <v>41.528</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>41.864375</v>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
@@ -39324,15 +38928,11 @@
           <t>40.9025</t>
         </is>
       </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>41.57</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>41.88125</t>
-        </is>
+      <c r="AN101" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>41.88125</v>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
@@ -39711,15 +39311,11 @@
           <t>42.9075</t>
         </is>
       </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>41.217</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>40.544375</t>
-        </is>
+      <c r="AN102" t="n">
+        <v>41.217</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>40.544375</v>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
@@ -40098,15 +39694,11 @@
           <t>42.7025</t>
         </is>
       </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>41.152</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>40.455625</t>
-        </is>
+      <c r="AN103" t="n">
+        <v>41.152</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>40.455625</v>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
@@ -40485,15 +40077,11 @@
           <t>42.4325</t>
         </is>
       </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>41.08</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>40.359375</t>
-        </is>
+      <c r="AN104" t="n">
+        <v>41.08</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>40.359375</v>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
@@ -40872,15 +40460,11 @@
           <t>42.17749999999999</t>
         </is>
       </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>41.003</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>40.2775</t>
-        </is>
+      <c r="AN105" t="n">
+        <v>41.003</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>40.2775</v>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
@@ -41259,15 +40843,11 @@
           <t>41.85</t>
         </is>
       </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>40.92</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>40.189375</t>
-        </is>
+      <c r="AN106" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>40.189375</v>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
@@ -41646,15 +41226,11 @@
           <t>41.5225</t>
         </is>
       </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>40.833</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>40.085625</t>
-        </is>
+      <c r="AN107" t="n">
+        <v>40.833</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>40.085625</v>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
@@ -42033,15 +41609,11 @@
           <t>41.15750000000001</t>
         </is>
       </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>40.699</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>39.954375</t>
-        </is>
+      <c r="AN108" t="n">
+        <v>40.699</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>39.954375</v>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
@@ -42420,15 +41992,11 @@
           <t>40.88</t>
         </is>
       </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>40.595</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>39.85875</t>
-        </is>
+      <c r="AN109" t="n">
+        <v>40.595</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>39.85875</v>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
@@ -42807,15 +42375,11 @@
           <t>40.645</t>
         </is>
       </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>40.522</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>39.775625</t>
-        </is>
+      <c r="AN110" t="n">
+        <v>40.522</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>39.775625</v>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
@@ -43194,15 +42758,11 @@
           <t>40.395</t>
         </is>
       </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>40.435</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>39.67874999999999</t>
-        </is>
+      <c r="AN111" t="n">
+        <v>40.435</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>39.67874999999999</v>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
@@ -43581,15 +43141,11 @@
           <t>14.2575</t>
         </is>
       </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>14.387</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>14.425</t>
-        </is>
+      <c r="AN112" t="n">
+        <v>14.387</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>14.425</v>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
@@ -43968,15 +43524,11 @@
           <t>14.27</t>
         </is>
       </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>14.387</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>14.434375</t>
-        </is>
+      <c r="AN113" t="n">
+        <v>14.387</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>14.434375</v>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
@@ -44355,15 +43907,11 @@
           <t>14.2825</t>
         </is>
       </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>14.388</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>14.445</t>
-        </is>
+      <c r="AN114" t="n">
+        <v>14.388</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>14.445</v>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
@@ -44742,15 +44290,11 @@
           <t>14.3075</t>
         </is>
       </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>14.39</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>14.45875</t>
-        </is>
+      <c r="AN115" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>14.45875</v>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
@@ -45129,15 +44673,11 @@
           <t>14.33</t>
         </is>
       </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>14.392</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>14.4675</t>
-        </is>
+      <c r="AN116" t="n">
+        <v>14.392</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>14.4675</v>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
@@ -45516,15 +45056,11 @@
           <t>14.345</t>
         </is>
       </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>14.393</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>14.475625</t>
-        </is>
+      <c r="AN117" t="n">
+        <v>14.393</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>14.475625</v>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
@@ -45903,15 +45439,11 @@
           <t>14.3575</t>
         </is>
       </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>14.392</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>14.480625</t>
-        </is>
+      <c r="AN118" t="n">
+        <v>14.392</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>14.480625</v>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
@@ -46290,15 +45822,11 @@
           <t>14.3775</t>
         </is>
       </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>14.394</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>14.490625</t>
-        </is>
+      <c r="AN119" t="n">
+        <v>14.394</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>14.490625</v>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
@@ -46677,15 +46205,11 @@
           <t>14.4</t>
         </is>
       </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>14.398</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>14.501875</t>
-        </is>
+      <c r="AN120" t="n">
+        <v>14.398</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>14.501875</v>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
@@ -47064,15 +46588,11 @@
           <t>14.4275</t>
         </is>
       </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>14.402</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>14.513125</t>
-        </is>
+      <c r="AN121" t="n">
+        <v>14.402</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>14.513125</v>
       </c>
       <c r="AP121" t="inlineStr">
         <is>

--- a/Result/checksun/油電燃氣業.xlsx
+++ b/Result/checksun/油電燃氣業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1725,7 +1725,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2151,7 +2151,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2575,7 +2575,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>9937</t>
@@ -2997,7 +3001,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>9937</t>
@@ -3419,7 +3427,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>9937</t>
@@ -3841,7 +3853,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>9937</t>
@@ -4263,7 +4279,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>9937</t>
@@ -4685,7 +4705,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>9937</t>
@@ -5107,7 +5131,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>9937</t>
@@ -5531,7 +5559,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【d2】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5957,7 +5985,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6383,7 +6411,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6809,7 +6837,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7235,7 +7263,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7661,7 +7689,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8087,7 +8115,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8513,7 +8541,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8939,7 +8967,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9365,7 +9393,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9791,7 +9819,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10217,7 +10245,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10643,7 +10671,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11069,7 +11097,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11495,7 +11523,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11921,7 +11949,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12347,7 +12375,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12773,7 +12801,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13199,7 +13227,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13625,7 +13653,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14049,7 +14077,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>9926</t>
@@ -14471,7 +14503,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>9926</t>
@@ -19579,7 +19615,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>【b1】</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>9908</t>
@@ -23837,7 +23877,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24261,7 +24301,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>8931</t>
@@ -24683,7 +24727,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>8931</t>
@@ -25105,7 +25153,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>8931</t>
@@ -25527,7 +25579,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>8931</t>
@@ -25949,7 +26005,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>8931</t>
@@ -28929,7 +28989,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29355,7 +29415,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -29781,7 +29841,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30207,7 +30267,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -30631,7 +30691,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>8927</t>
@@ -31053,7 +31117,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>8927</t>
@@ -31475,7 +31543,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>8927</t>
@@ -31897,7 +31969,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>8927</t>
@@ -32319,7 +32395,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>8927</t>
@@ -32741,7 +32821,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>8927</t>
@@ -33163,7 +33247,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>8927</t>
@@ -33585,7 +33673,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>8926</t>
@@ -34015,7 +34107,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>8926</t>
@@ -38351,7 +38447,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>8917</t>
@@ -38773,7 +38873,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>8917</t>
@@ -39195,7 +39299,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>8917</t>
@@ -39617,7 +39725,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>8917</t>
@@ -40041,7 +40153,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -40467,7 +40579,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -40891,7 +41003,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>8917</t>
@@ -41313,7 +41429,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>8917</t>
@@ -41735,7 +41855,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>8917</t>
@@ -42157,7 +42281,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>8917</t>
@@ -52390,7 +52518,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -52817,7 +52945,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -53244,7 +53372,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -53669,7 +53797,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>2616</t>
@@ -54092,7 +54224,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>2616</t>
